--- a/output/upload/S00027_2243_간편가입_경영인H정기보험_무배당.xlsx
+++ b/output/upload/S00027_2243_간편가입_경영인H정기보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW50"/>
+  <dimension ref="A1:AW72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
@@ -2729,11 +2729,11 @@
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
@@ -2794,29 +2794,29 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N9" s="6" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -2895,11 +2895,11 @@
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
@@ -2960,29 +2960,29 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N11" s="6" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -3053,11 +3053,11 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L12" s="6" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -3126,29 +3126,29 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N13" s="6" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
@@ -3209,29 +3209,29 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" s="6" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3306,11 +3306,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3333,29 +3333,29 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3531,11 +3531,11 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -3558,29 +3558,29 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -3648,29 +3648,29 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3703,11 +3703,11 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -3738,29 +3738,29 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -3783,29 +3783,29 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3846,11 +3846,11 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -3873,29 +3873,29 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4071,11 +4071,11 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -4098,29 +4098,29 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4161,11 +4161,11 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -4188,29 +4188,29 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4243,11 +4243,11 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -4278,29 +4278,29 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -4323,29 +4323,29 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4386,11 +4386,11 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -4413,29 +4413,29 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4611,11 +4611,11 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -4638,29 +4638,29 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4701,11 +4701,11 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -4728,29 +4728,29 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4783,11 +4783,11 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -4818,29 +4818,29 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4863,31 +4863,1021 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>90</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>999</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
           <t>N0</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>999</v>
-      </c>
-      <c r="M50" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>90</v>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="N50" t="n">
+      <c r="N51" t="n">
         <v>0</v>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>999</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>999</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>999</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>999</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>999</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>90</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>90</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>90</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>999</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>90</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>999</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>999</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>999</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>999</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>999</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>90</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>90</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>90</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>999</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>90</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>999</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>999</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>999</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>999</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>999</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>90</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>90</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>90</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>999</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>90</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>999</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>999</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>999</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>999</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>999</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>

--- a/output/upload/S00027_2243_간편가입_경영인H정기보험_무배당.xlsx
+++ b/output/upload/S00027_2243_간편가입_경영인H정기보험_무배당.xlsx
@@ -2611,11 +2611,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2694,11 +2714,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2777,11 +2817,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2860,11 +2920,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2943,11 +3023,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3026,11 +3126,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3109,11 +3229,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3192,11 +3332,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3274,8 +3434,31 @@
       <c r="AW14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3319,8 +3502,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3364,8 +3570,31 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3409,8 +3638,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3454,8 +3706,31 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3499,8 +3774,31 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3544,8 +3842,31 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3589,8 +3910,31 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3634,8 +3978,31 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3679,8 +4046,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3724,8 +4114,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3769,8 +4182,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3814,8 +4250,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3859,8 +4318,31 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3904,8 +4386,31 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3949,8 +4454,31 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3994,8 +4522,31 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4039,8 +4590,31 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4084,8 +4658,31 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4129,8 +4726,31 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4174,8 +4794,31 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4219,8 +4862,31 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4264,8 +4930,31 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4309,8 +4998,31 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4354,8 +5066,31 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4399,8 +5134,31 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4444,8 +5202,31 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4489,8 +5270,31 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4534,8 +5338,31 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4579,8 +5406,31 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4624,8 +5474,31 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4669,8 +5542,31 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4714,8 +5610,31 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4759,8 +5678,31 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4804,8 +5746,31 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4849,8 +5814,31 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4894,8 +5882,31 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4939,8 +5950,31 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4984,8 +6018,31 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5029,8 +6086,31 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5074,8 +6154,31 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5119,8 +6222,31 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5164,8 +6290,31 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5209,8 +6358,31 @@
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5254,8 +6426,31 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5299,8 +6494,31 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5344,8 +6562,31 @@
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5389,8 +6630,31 @@
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5434,8 +6698,31 @@
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5479,8 +6766,31 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5524,8 +6834,31 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5569,8 +6902,31 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5614,8 +6970,31 @@
       </c>
     </row>
     <row r="67">
-      <c r="B67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5659,8 +7038,31 @@
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5704,8 +7106,31 @@
       </c>
     </row>
     <row r="69">
-      <c r="B69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5749,8 +7174,31 @@
       </c>
     </row>
     <row r="70">
-      <c r="B70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5794,8 +7242,31 @@
       </c>
     </row>
     <row r="71">
-      <c r="B71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5839,8 +7310,31 @@
       </c>
     </row>
     <row r="72">
-      <c r="B72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2243A01</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>22431</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00027_2243_간편가입_경영인H정기보험_무배당.xlsx
+++ b/output/upload/S00027_2243_간편가입_경영인H정기보험_무배당.xlsx
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">

--- a/output/upload/S00027_2243_간편가입_경영인H정기보험_무배당.xlsx
+++ b/output/upload/S00027_2243_간편가입_경영인H정기보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW72"/>
+  <dimension ref="A1:AW50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
@@ -2769,11 +2769,11 @@
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N8" s="6" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
@@ -2854,29 +2854,29 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -2975,11 +2975,11 @@
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N10" s="6" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
@@ -3060,29 +3060,29 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N11" s="6" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -3173,11 +3173,11 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" s="6" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -3266,29 +3266,29 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N13" s="6" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
@@ -3369,29 +3369,29 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L14" s="6" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N14" s="6" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3489,11 +3489,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3539,29 +3539,29 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3829,11 +3829,11 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -3879,29 +3879,29 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3965,11 +3965,11 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -4015,29 +4015,29 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4093,11 +4093,11 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -4151,29 +4151,29 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -4219,29 +4219,29 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -4305,11 +4305,11 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -4355,29 +4355,29 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4645,11 +4645,11 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -4695,29 +4695,29 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4781,11 +4781,11 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -4831,29 +4831,29 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4909,11 +4909,11 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -4967,29 +4967,29 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -5035,29 +5035,29 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5121,11 +5121,11 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -5171,29 +5171,29 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5461,11 +5461,11 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -5511,29 +5511,29 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -5597,11 +5597,11 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -5647,29 +5647,29 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5725,11 +5725,11 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -5783,29 +5783,29 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -5851,1527 +5851,31 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O50" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>90</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>999</v>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N52" t="n">
-        <v>999</v>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
-        <v>999</v>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N53" t="n">
-        <v>999</v>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
-        <v>999</v>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>90</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N55" t="n">
-        <v>90</v>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>90</v>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N56" t="n">
-        <v>999</v>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
-        <v>90</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
-        <v>999</v>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N58" t="n">
-        <v>999</v>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>999</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N59" t="n">
-        <v>999</v>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>999</v>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
-        <v>90</v>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N61" t="n">
-        <v>90</v>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>90</v>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N62" t="n">
-        <v>999</v>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L63" t="n">
-        <v>90</v>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L64" t="n">
-        <v>999</v>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N64" t="n">
-        <v>999</v>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>999</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N65" t="n">
-        <v>999</v>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L66" t="n">
-        <v>999</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>90</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N67" t="n">
-        <v>90</v>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L68" t="n">
-        <v>90</v>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N68" t="n">
-        <v>999</v>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L69" t="n">
-        <v>90</v>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L70" t="n">
-        <v>999</v>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N70" t="n">
-        <v>999</v>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L71" t="n">
-        <v>999</v>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N71" t="n">
-        <v>999</v>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L72" t="n">
-        <v>999</v>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>

--- a/output/upload/S00027_2243_간편가입_경영인H정기보험_무배당.xlsx
+++ b/output/upload/S00027_2243_간편가입_경영인H정기보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW50"/>
+  <dimension ref="A1:AW14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -3025,22 +3025,22 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2243A01</t>
+          <t>2243A02</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>2243001</t>
+          <t>2243002</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3128,22 +3128,22 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2243A01</t>
+          <t>2243A02</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>2243001</t>
+          <t>2243002</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -3231,22 +3231,22 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2243A01</t>
+          <t>2243A02</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>2243001</t>
+          <t>2243002</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -3334,22 +3334,22 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2243A01</t>
+          <t>2243A02</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>2243001</t>
+          <t>2243002</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3433,2454 +3433,6 @@
       <c r="AV14" s="6" t="n"/>
       <c r="AW14" s="6" t="n"/>
     </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>90</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>90</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>90</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>999</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>999</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>999</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>90</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>90</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>90</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>999</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N21" t="n">
-        <v>999</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>999</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>90</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>90</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>90</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>999</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N25" t="n">
-        <v>999</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>999</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>90</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N27" t="n">
-        <v>90</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>90</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>999</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N29" t="n">
-        <v>999</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>999</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>90</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N31" t="n">
-        <v>90</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>90</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>999</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N33" t="n">
-        <v>999</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>999</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>90</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N35" t="n">
-        <v>90</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>90</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>999</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N37" t="n">
-        <v>999</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>999</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>90</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N39" t="n">
-        <v>90</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>90</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>999</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N41" t="n">
-        <v>999</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>999</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>90</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N43" t="n">
-        <v>90</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>90</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>999</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N45" t="n">
-        <v>999</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
-        <v>999</v>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
-        <v>90</v>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N47" t="n">
-        <v>90</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
-        <v>90</v>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L49" t="n">
-        <v>999</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N49" t="n">
-        <v>999</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>999</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="I3:N3"/>

--- a/output/upload/S00027_2243_간편가입_경영인H정기보험_무배당.xlsx
+++ b/output/upload/S00027_2243_간편가입_경영인H정기보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -2716,22 +2716,22 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2243A01</t>
+          <t>2243A02</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>2243001</t>
+          <t>2243002</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
+          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
@@ -2769,11 +2769,11 @@
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
@@ -2817,72 +2817,20 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="6" t="n"/>
       <c r="P9" s="6" t="n"/>
       <c r="Q9" s="6" t="n"/>
       <c r="R9" s="6" t="n"/>
@@ -2920,72 +2868,20 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>2243A01</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>2243001</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 1종(5%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
+      <c r="N10" s="6" t="n"/>
+      <c r="O10" s="6" t="n"/>
       <c r="P10" s="6" t="n"/>
       <c r="Q10" s="6" t="n"/>
       <c r="R10" s="6" t="n"/>
@@ -3023,72 +2919,20 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>2243A02</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>2243002</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="O11" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="n"/>
+      <c r="N11" s="6" t="n"/>
+      <c r="O11" s="6" t="n"/>
       <c r="P11" s="6" t="n"/>
       <c r="Q11" s="6" t="n"/>
       <c r="R11" s="6" t="n"/>
@@ -3126,72 +2970,20 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>2243A02</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>2243002</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>X90</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n"/>
+      <c r="N12" s="6" t="n"/>
+      <c r="O12" s="6" t="n"/>
       <c r="P12" s="6" t="n"/>
       <c r="Q12" s="6" t="n"/>
       <c r="R12" s="6" t="n"/>
@@ -3229,72 +3021,20 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>2243A02</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>2243002</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="O13" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n"/>
+      <c r="M13" s="6" t="n"/>
+      <c r="N13" s="6" t="n"/>
+      <c r="O13" s="6" t="n"/>
       <c r="P13" s="6" t="n"/>
       <c r="Q13" s="6" t="n"/>
       <c r="R13" s="6" t="n"/>
@@ -3332,72 +3072,20 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>2243A02</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>2243002</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 경영인H정기보험 무배당 보장형 계약 2종(10%체증형) 해약환급금 일부지급형</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="M14" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
+      <c r="N14" s="6" t="n"/>
+      <c r="O14" s="6" t="n"/>
       <c r="P14" s="6" t="n"/>
       <c r="Q14" s="6" t="n"/>
       <c r="R14" s="6" t="n"/>
